--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shinj\Desktop\work\Edu\English\sight words\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{263BBB7D-1778-40C2-B8A4-B642DF60A674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DEA806-D0B1-465C-814A-08130FCDA700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{877E2AFA-B88B-4233-8CB7-67C5A8571A6B}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="321">
   <si>
     <t>I am hungry</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -380,6 +380,941 @@
   <si>
     <t>우리는 학교에 있어요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>in</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>under</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>are</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>where</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~안에</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~아래에</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~이다. 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어디에</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>It is under the bed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Where are you?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I am in my room</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Are you hungry?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것은 침대 아래에 있어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너 어디 있어?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 내 방 안에 있어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너 배고프니?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>help</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>me</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>just</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돕다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나를, 나에게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그저, 단지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>They love me</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>It is a wolf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I'm just looking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그들은 나를 사랑해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것은 늑대 한마리이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저는 그냥 구경하고 있어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나 좀 도와줘.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Help me, please.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>right</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>its</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>what</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>긴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맞는, 오른쪽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무엇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>That's right</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>It has long ears.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Its tail is long.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>What is your name?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것은 맞아.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것은 긴 귀를 갖고 있어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것의 꼬리는 길어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너의 이름은 뭐야?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>this</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>that</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>good</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>both</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이것, 이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저것, 저~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋은</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>둘다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>You are a good boy.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>This is my pencil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>We are both happy.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Is that your hat?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 착한(좋은) 아이야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리는 둘다 행복해.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저것은 너의 모자야?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ride</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>start</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>try</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>will</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시작하다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노력하다, 해 보다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~할 것이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>They start to run.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>You will like it.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>열심히 노력해!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Try hard!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그들은 달리기 시작한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스케이트보드 타자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 그것을 좋아할 거야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>come</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>up</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>down</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자라다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위로,위에</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아래로, 아래에</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sit down</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stand up.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Come home early.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>They will grow big.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(아래로)앉아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(위에)일어서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>집에 일찍 와</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것들은 크게 자랄 거예요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>want</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>look</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>which</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>then</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>원하다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보다. 보이다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어느, 어떤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그러면, 그다음에</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>You look funny.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Which one do you want?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I want this bag.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I came first, then Ann.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너 우스꽝스러워 보여.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 어느 것을 원해?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>run</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>get</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>away</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달리다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>멈추다, 멈춤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>받다, 얻다, 잡다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>떨어진 곳에, 다른데(로)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stop crying!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Let's run to the house.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Run away!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그만 울어!(울음을 멈춰!)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 선물을 받고 싶어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(다른 데로) 도망가!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>on</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>make</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>put</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>some</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~위에</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>만들다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>놓다, 두다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금, 약간의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Have some bread.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>It's on the table.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Put in the bag.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빵을 좀 먹어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것은 탁자 위에 있어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것을 가방 안에 넣어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>샌드위치를 만들자.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>show</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>only</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>but</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>so</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정말, 그렇게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보여주다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유일한, 겨우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하지만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>It is so pretty.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He is only 5.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Show me your ticket.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>It is small but strong.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것은 정말 예뻐.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그는 겨우 다섯 살이야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당신의 표를 보여 주세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것은 작지만 힘이 세.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>have</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>read</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>again</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>into</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가지고 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>읽다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다시, 또</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~안으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I have a brother.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I'm late again.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He went into the cave.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 형이 있어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것을 같이 읽자.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 또 늦었어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그는 동굴 안으로 들어갔다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>say</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ask</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>better</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>together</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>말하다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>묻다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 좋은</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>함께, 같이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ask me anything.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I feel better now</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Let's make it together.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>What did you say?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나에게 뭐든 물어봐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 몸이 더 좋아졌어요(나았어요)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것을 같이 만들자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너 뭐라고 말했어?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>see</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>any</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>find</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>found</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보다, 보이다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>약간의, 조금도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찾다, 발견하다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찾았다, 발견했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I see a bird.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Let's find some buds.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I don't have any money.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 새가 보여.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>벌레들을 좀 찾아보자.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 돈이 조금도 없어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그는 보물을 찾았다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>new</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>old</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>she</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>has</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새로운</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오래된, 늙은</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그녀는</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>She is my mom.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Her bike is new.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>She has a doll.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>My bike is old.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그녀는 우리 엄마예요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내 자건거는 낡았어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그녀는 인형이 있어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그녀의 자전거는 새 거야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>these</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>those</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>made</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>who</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이것들, 이~(여러 개를 가리킬 때)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저것들, 저~(여러 개를 가리킬 때)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Who are they?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>We made a castle.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Look at those clouds!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I want these cookies.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저 애들은 누구야?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리는 성을 만들었어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저 구름들 좀 봐!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 이 쿠키들이 먹고 싶어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이건은 내 연필이야.</t>
+  </si>
+  <si>
+    <t>Let's ride skateboards.</t>
+  </si>
+  <si>
+    <t>나는 이 가방을 원해요.(갖고 싶어요.)</t>
+  </si>
+  <si>
+    <t>내가 맨 먼저 왔고, 그 다음에 엔이 왔어.</t>
+  </si>
+  <si>
+    <t>집까지 달리자.</t>
+  </si>
+  <si>
+    <t>I want to get a present.</t>
+  </si>
+  <si>
+    <t>Let's make a sandwich.</t>
+  </si>
+  <si>
+    <t>Let's read it together.</t>
+  </si>
+  <si>
+    <t>He found treasure.</t>
   </si>
 </sst>
 </file>
@@ -766,12 +1701,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF64EC60-60F9-4E2B-B641-C5E981778C27}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1006,6 +1941,666 @@
       </c>
       <c r="C21" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>124</v>
+      </c>
+      <c r="C30" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>140</v>
+      </c>
+      <c r="C34" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>141</v>
+      </c>
+      <c r="C35" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>158</v>
+      </c>
+      <c r="C38" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>155</v>
+      </c>
+      <c r="C39" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>313</v>
+      </c>
+      <c r="C40" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>156</v>
+      </c>
+      <c r="C41" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>170</v>
+      </c>
+      <c r="C42" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>172</v>
+      </c>
+      <c r="C44" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>173</v>
+      </c>
+      <c r="C45" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>186</v>
+      </c>
+      <c r="C46" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>187</v>
+      </c>
+      <c r="C47" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>188</v>
+      </c>
+      <c r="C48" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>189</v>
+      </c>
+      <c r="C49" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>200</v>
+      </c>
+      <c r="C50" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>201</v>
+      </c>
+      <c r="C51" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>317</v>
+      </c>
+      <c r="C52" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>202</v>
+      </c>
+      <c r="C53" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C54" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>215</v>
+      </c>
+      <c r="C55" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>216</v>
+      </c>
+      <c r="C56" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>318</v>
+      </c>
+      <c r="C57" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>229</v>
+      </c>
+      <c r="C58" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>230</v>
+      </c>
+      <c r="C59" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>231</v>
+      </c>
+      <c r="C60" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>232</v>
+      </c>
+      <c r="C61" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>245</v>
+      </c>
+      <c r="C62" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>319</v>
+      </c>
+      <c r="C63" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>246</v>
+      </c>
+      <c r="C64" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>247</v>
+      </c>
+      <c r="C65" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>260</v>
+      </c>
+      <c r="C66" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>261</v>
+      </c>
+      <c r="C67" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>262</v>
+      </c>
+      <c r="C68" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>263</v>
+      </c>
+      <c r="C69" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>276</v>
+      </c>
+      <c r="C70" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>277</v>
+      </c>
+      <c r="C71" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>278</v>
+      </c>
+      <c r="C72" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>320</v>
+      </c>
+      <c r="C73" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>290</v>
+      </c>
+      <c r="C74" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>293</v>
+      </c>
+      <c r="C75" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>292</v>
+      </c>
+      <c r="C76" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>291</v>
+      </c>
+      <c r="C77" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>304</v>
+      </c>
+      <c r="C78" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>305</v>
+      </c>
+      <c r="C79" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>306</v>
+      </c>
+      <c r="C80" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>307</v>
+      </c>
+      <c r="C81" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -1016,10 +2611,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A662D3C5-D1D0-4A47-8623-A995CF218025}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1253,6 +2848,666 @@
         <v>76</v>
       </c>
     </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>119</v>
+      </c>
+      <c r="C33" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>135</v>
+      </c>
+      <c r="C37" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>147</v>
+      </c>
+      <c r="C38" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>148</v>
+      </c>
+      <c r="C39" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>149</v>
+      </c>
+      <c r="C40" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>162</v>
+      </c>
+      <c r="C42" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>163</v>
+      </c>
+      <c r="C43" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>164</v>
+      </c>
+      <c r="C44" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>165</v>
+      </c>
+      <c r="C45" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>178</v>
+      </c>
+      <c r="C46" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>179</v>
+      </c>
+      <c r="C47" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>180</v>
+      </c>
+      <c r="C48" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>181</v>
+      </c>
+      <c r="C49" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>192</v>
+      </c>
+      <c r="C50" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>193</v>
+      </c>
+      <c r="C51" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>194</v>
+      </c>
+      <c r="C52" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>195</v>
+      </c>
+      <c r="C53" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>206</v>
+      </c>
+      <c r="C54" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>207</v>
+      </c>
+      <c r="C55" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>208</v>
+      </c>
+      <c r="C56" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>209</v>
+      </c>
+      <c r="C57" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>224</v>
+      </c>
+      <c r="C58" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>221</v>
+      </c>
+      <c r="C59" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>222</v>
+      </c>
+      <c r="C60" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>223</v>
+      </c>
+      <c r="C61" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>237</v>
+      </c>
+      <c r="C62" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>238</v>
+      </c>
+      <c r="C63" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>239</v>
+      </c>
+      <c r="C64" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>240</v>
+      </c>
+      <c r="C65" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>252</v>
+      </c>
+      <c r="C66" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>253</v>
+      </c>
+      <c r="C67" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>254</v>
+      </c>
+      <c r="C68" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>255</v>
+      </c>
+      <c r="C69" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>268</v>
+      </c>
+      <c r="C70" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>269</v>
+      </c>
+      <c r="C71" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>270</v>
+      </c>
+      <c r="C72" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>271</v>
+      </c>
+      <c r="C73" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>283</v>
+      </c>
+      <c r="C74" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>284</v>
+      </c>
+      <c r="C75" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>285</v>
+      </c>
+      <c r="C76" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>286</v>
+      </c>
+      <c r="C77" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>298</v>
+      </c>
+      <c r="C78" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>299</v>
+      </c>
+      <c r="C79" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>300</v>
+      </c>
+      <c r="C80" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>301</v>
+      </c>
+      <c r="C81" t="s">
+        <v>301</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shinj\Desktop\work\Edu\English\sight words\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DEA806-D0B1-465C-814A-08130FCDA700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24260D91-B831-4DA7-A7A1-E8120B621AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{877E2AFA-B88B-4233-8CB7-67C5A8571A6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{877E2AFA-B88B-4233-8CB7-67C5A8571A6B}"/>
   </bookViews>
   <sheets>
     <sheet name="문장" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="639">
   <si>
     <t>I am hungry</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -490,10 +490,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>그것은 늑대 한마리이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>저는 그냥 구경하고 있어요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1222,10 +1218,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내 자건거는 낡았어.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>그녀는 인형이 있어.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1315,6 +1307,1272 @@
   </si>
   <si>
     <t>He found treasure.</t>
+  </si>
+  <si>
+    <t>cut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">the </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>open</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>was</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>만들었다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자르다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그,이,저</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>열다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~였다, 있었다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Who is the man?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Open the window, please.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I was so happy.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Let's cut the cake.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저 남자는 누구야?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>창문을 좀 열어 주세요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 무척 행복했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>케이크를 자르다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>they</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>went</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>saw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>were</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그들은, 그것들은</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>갔다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>봤다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~였다, 있었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I went to the zoo today.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I saw many animals.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>They are so cute.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>They were so pretty.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 오늘 동물원에 갔다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 많은 동물들을 봤다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것들은 정말 귀여워</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>be</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>how</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>never</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~이다, ~이 되다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어떻게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>절대/결코~않다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tell me the answer.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I want to be a singer.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Never tell a lie.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>How is the weather today?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나에게 답을 말해 줘.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 가수가 되고 싶어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>절대 거짓말하지 마.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘 날씨 어때요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>his</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>live</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>many</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>살다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>많은</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밖에, 밖으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I am his dad.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I want to live here.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Let's eat out tonight.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>There are so many cars.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 그의 아빠예요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 여기에 살고 싶어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘밤에 밖에서 먹자.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아주 많은 차들이 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>work</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>first.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일하다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>들고 있다, 나르다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~처럼, ~만큼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>as</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jane came first</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제인이 맨 먼저 왔다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>We work on a farm.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Help me carry the bags.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>It's as sweet as honey.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리는 농장에서 일해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내가 봉투 나르는 것 좀 도와줘.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이것은 꿀처럼 달아요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>play</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>with</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>walk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>don't</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>놀다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~와 함께</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>걷다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~하지 않다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Play with me, Dad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I don't like milk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I live with my parents.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나와 같이 놀아요, 아빠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>집에 걸어가자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 우유를 안 좋아해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 부모님과 함께 살아요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>our</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>their</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>little</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>no</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그들의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니, 안돼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>This is our house</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Look at the little bug.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Their house is big.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No, I don't want it.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이건 우리의 집이에요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저 작은 벌레 좀 봐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그들의 집은 커요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니, 난 그것을 원하지 않아.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>do</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>every</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>after</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>from</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~후에</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~(에서)부터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I play soccer after school.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I do my homework at 4.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He sleeps from 9 to 7.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 방과 후에 축구를 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 매일 피아노를 친다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 4시에 숙제를 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그는 9시부터 7시까지 잔다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>첫 번 째의, 맨 먼저</t>
+  </si>
+  <si>
+    <t>call</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>him</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>why</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>came</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부르다, 전화하다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그를, 그에게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>왜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>왔다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I will ask him</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>why are you late.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>call me Emily.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The bus came late.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내가 그에게 물어볼께.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 왜 늦었어?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버스가 늦게 왔다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>know</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>her</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>must</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>before</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그녀를, 그녀에게, 그녀의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~해야 되다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~전에</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Do you know her?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I don't like her.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I must go home now.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Come back before dinner.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 그녀를 알아?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 그녀를 안 좋아해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 지금 집에 가야 해.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁 먹기 전에 돌아와</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>for</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>write</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>use</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>when</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~을 위해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쓰다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용하다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>언제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>He can write I English</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>This is for you.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>When do you get up.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>You can use my phone.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그는 영어로 쓸 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이것은 너를 위한 거야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 언제 일어나?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 내 핸드폰을 써도 돼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>much</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>always</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>more</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>먹다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>많은, 많이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 많은</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Let's eat some chicken.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Don't eat too much</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Can I eat more pizza?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>She is always kind.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>치킨을 먹자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너무 많이 먹지 마.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저 피자 더 먹어도 돼요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그녀는 항상 친절해.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>very</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>now</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>keep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>got</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매우,아주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금, 이제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유지하다, 기르다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>받았다. 생겼다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>It's very tall.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>What time is it now?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Can I keep this dog?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>You got a new bat!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것은 아주 높아요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금 몇 시예요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너 새 야구 방망이가 생겼구나!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>by</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>there</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>does</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>앉다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~옆에</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거기에, 저기에</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I know the man over there.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sit by me.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Come and sit there.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내 옆에 앉아.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 저기에 있는 남자를 알아.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>와서 여기 앉아.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그녀는 설거지를 해요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>best</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>give</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>us</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최고의, 제일 좋은</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>친절하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리를, 우리에게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>You are so kind.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I'll give you this flower.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mom made us cookies.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>You are the best</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 정말 친절하구나.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너에게 이 꽃을 줄게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엄마는 우리에게 쿠키를 만들어 주셨다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네가 최고야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>take</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>them</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>soon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~로, ~에게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그들을, 그들에게, 그것들을, 그것들에게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가지고 가다, 데리고 가다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>곧, 빨리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Let’s go to the park.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I'll be back soon,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I'll take them to grandma.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 어제 그것들을 봤어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공원으로 가자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금방 돌아올게.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>did</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>had</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>light</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>well</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>볼, 가벼운</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>We had a great day.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Turn off the light, please.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Did you have lunch?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sleep well, honey!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리는 즐거운 하루를 가졌다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불 좀 꺼 줘.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너 점심 먹었어?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잘자, 예쁜이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>if</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>let</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hurt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>please</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(만약)~하면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~하게 하다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아프다, 다치다, 다친</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제발, 부디</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I was hurt today.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Let me help you.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>If it snows, let's make a snowman.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 오늘 다쳤다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내가 너를 도와줄게.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>눈이 온다면 눈사람을 만들자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>all</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>of</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>one</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든,모두</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하나</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응, 네</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I want all of them.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yes, I can.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Just pick one color.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>What is the color of your car?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응, 나는 할 수 있어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 저것들을 모두 갖고 싶어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 가지 색만 골라</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당신 차의 색은 뭐예요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>two</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>or</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>about</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>둘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>또는, 아니면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생각하다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~에 대해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I have two books.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I thick this one is better.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>This story is about ghosts.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 책이 두 권 있어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나는 이제 더 좋다고 생각해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 이야기는 유령들에게 대한 것이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 축구가 좋아? 아니면 야구가 좋아?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것은 늑대 한 마리이다.</t>
+  </si>
+  <si>
+    <t>내 자전거는 낡았어.</t>
+  </si>
+  <si>
+    <t>그것들은 무척 예뻤다.</t>
+  </si>
+  <si>
+    <t>Let's walk home.</t>
+  </si>
+  <si>
+    <t>I play the piano every day.</t>
+  </si>
+  <si>
+    <t>나를 에밀리라고 불러줘</t>
+  </si>
+  <si>
+    <t>제가 이 개를 길러도 돼요?</t>
+  </si>
+  <si>
+    <t>She does the dishes.</t>
+  </si>
+  <si>
+    <t>I saw them yesterday.</t>
+  </si>
+  <si>
+    <t>내가 그것들을 할머니에게 가져가 드릴 게요.</t>
+  </si>
+  <si>
+    <t>Cluse the window, Please.</t>
+  </si>
+  <si>
+    <t>Do you like soccer or baseball?</t>
+  </si>
+  <si>
+    <t>가졌다</t>
   </si>
 </sst>
 </file>
@@ -1701,11 +2959,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF64EC60-60F9-4E2B-B641-C5E981778C27}">
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D161"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="24.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2006,7 +3264,7 @@
         <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>626</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -2017,7 +3275,7 @@
         <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -2025,10 +3283,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -2036,10 +3294,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -2047,10 +3305,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -2058,10 +3316,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -2069,10 +3327,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -2080,10 +3338,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -2091,10 +3349,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C35" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -2102,10 +3360,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -2113,10 +3371,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -2124,10 +3382,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C38" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -2135,10 +3393,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C39" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -2146,10 +3404,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -2157,10 +3415,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C41" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -2168,10 +3426,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -2179,10 +3437,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -2190,10 +3448,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C44" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -2201,10 +3459,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C45" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -2212,10 +3470,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C46" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -2223,10 +3481,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C47" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -2234,10 +3492,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C48" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -2245,10 +3503,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C49" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -2256,10 +3514,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C50" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -2267,10 +3525,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C51" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -2278,10 +3536,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C52" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -2289,10 +3547,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C53" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -2300,10 +3558,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -2311,10 +3569,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C55" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -2322,10 +3580,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C56" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -2333,10 +3591,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C57" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -2344,10 +3602,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C58" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -2355,10 +3613,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -2366,10 +3624,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C60" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -2377,10 +3635,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C61" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -2388,10 +3646,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C62" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -2399,10 +3657,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C63" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -2410,10 +3668,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C64" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -2421,10 +3679,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -2432,10 +3690,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C66" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -2443,10 +3701,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C67" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -2454,10 +3712,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C68" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -2465,10 +3723,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C69" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -2476,10 +3734,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C70" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -2487,10 +3745,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C71" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -2498,10 +3756,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C72" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -2509,10 +3767,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C73" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -2520,10 +3778,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C74" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -2531,10 +3789,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C75" t="s">
-        <v>295</v>
+        <v>627</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -2542,10 +3800,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C76" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -2553,10 +3811,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C77" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -2564,10 +3822,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C78" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -2575,10 +3833,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C79" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
@@ -2586,10 +3844,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C80" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -2597,10 +3855,890 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C81" t="s">
-        <v>311</v>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>329</v>
+      </c>
+      <c r="C82" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>330</v>
+      </c>
+      <c r="C83" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>331</v>
+      </c>
+      <c r="C84" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>332</v>
+      </c>
+      <c r="C85" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>345</v>
+      </c>
+      <c r="C86" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>346</v>
+      </c>
+      <c r="C87" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>347</v>
+      </c>
+      <c r="C88" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>348</v>
+      </c>
+      <c r="C89" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>359</v>
+      </c>
+      <c r="C90" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>360</v>
+      </c>
+      <c r="C91" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>361</v>
+      </c>
+      <c r="C92" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>362</v>
+      </c>
+      <c r="C93" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>375</v>
+      </c>
+      <c r="C94" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>376</v>
+      </c>
+      <c r="C95" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>377</v>
+      </c>
+      <c r="C96" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>378</v>
+      </c>
+      <c r="C97" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>390</v>
+      </c>
+      <c r="C98" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>392</v>
+      </c>
+      <c r="C99" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>393</v>
+      </c>
+      <c r="C100" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>394</v>
+      </c>
+      <c r="C101" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>406</v>
+      </c>
+      <c r="C102" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>629</v>
+      </c>
+      <c r="C103" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>407</v>
+      </c>
+      <c r="C104" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>408</v>
+      </c>
+      <c r="C105" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>420</v>
+      </c>
+      <c r="C106" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>421</v>
+      </c>
+      <c r="C107" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>422</v>
+      </c>
+      <c r="C108" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>423</v>
+      </c>
+      <c r="C109" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>436</v>
+      </c>
+      <c r="C110" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>630</v>
+      </c>
+      <c r="C111" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>437</v>
+      </c>
+      <c r="C112" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>438</v>
+      </c>
+      <c r="C113" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>452</v>
+      </c>
+      <c r="C114" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>453</v>
+      </c>
+      <c r="C115" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>454</v>
+      </c>
+      <c r="C116" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>455</v>
+      </c>
+      <c r="C117" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>467</v>
+      </c>
+      <c r="C118" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>468</v>
+      </c>
+      <c r="C119" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>469</v>
+      </c>
+      <c r="C120" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>470</v>
+      </c>
+      <c r="C121" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>483</v>
+      </c>
+      <c r="C122" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>484</v>
+      </c>
+      <c r="C123" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>485</v>
+      </c>
+      <c r="C124" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>486</v>
+      </c>
+      <c r="C125" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>499</v>
+      </c>
+      <c r="C126" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>500</v>
+      </c>
+      <c r="C127" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>501</v>
+      </c>
+      <c r="C128" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>502</v>
+      </c>
+      <c r="C129" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>515</v>
+      </c>
+      <c r="C130" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>516</v>
+      </c>
+      <c r="C131" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>517</v>
+      </c>
+      <c r="C132" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>518</v>
+      </c>
+      <c r="C133" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>530</v>
+      </c>
+      <c r="C134" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>529</v>
+      </c>
+      <c r="C135" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>531</v>
+      </c>
+      <c r="C136" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>633</v>
+      </c>
+      <c r="C137" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>544</v>
+      </c>
+      <c r="C138" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>545</v>
+      </c>
+      <c r="C139" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>546</v>
+      </c>
+      <c r="C140" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>547</v>
+      </c>
+      <c r="C141" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>634</v>
+      </c>
+      <c r="C142" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>560</v>
+      </c>
+      <c r="C143" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>562</v>
+      </c>
+      <c r="C144" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>561</v>
+      </c>
+      <c r="C145" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>573</v>
+      </c>
+      <c r="C146" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>574</v>
+      </c>
+      <c r="C147" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>575</v>
+      </c>
+      <c r="C148" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>576</v>
+      </c>
+      <c r="C149" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>589</v>
+      </c>
+      <c r="C150" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>590</v>
+      </c>
+      <c r="C151" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>636</v>
+      </c>
+      <c r="C152" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>591</v>
+      </c>
+      <c r="C153" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>604</v>
+      </c>
+      <c r="C154" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>603</v>
+      </c>
+      <c r="C155" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>605</v>
+      </c>
+      <c r="C156" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>606</v>
+      </c>
+      <c r="C157" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>619</v>
+      </c>
+      <c r="C158" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
+        <v>620</v>
+      </c>
+      <c r="C159" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>621</v>
+      </c>
+      <c r="C160" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>637</v>
+      </c>
+      <c r="C161" t="s">
+        <v>625</v>
       </c>
     </row>
   </sheetData>
@@ -2611,7 +4749,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A662D3C5-D1D0-4A47-8623-A995CF218025}">
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C161"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
@@ -2941,10 +5079,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -2952,10 +5090,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -2963,10 +5101,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -2974,10 +5112,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -2985,10 +5123,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -2996,10 +5134,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -3007,10 +5145,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -3018,10 +5156,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -3029,10 +5167,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -3040,10 +5178,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C39" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -3051,10 +5189,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C40" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -3062,10 +5200,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -3073,10 +5211,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -3084,10 +5222,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C43" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -3095,10 +5233,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C44" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -3106,10 +5244,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C45" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -3117,10 +5255,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C46" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -3128,10 +5266,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C47" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -3139,10 +5277,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C48" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -3150,10 +5288,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C49" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -3161,10 +5299,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C50" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -3172,10 +5310,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C51" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -3183,10 +5321,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C52" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -3194,10 +5332,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C53" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -3205,10 +5343,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C54" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -3216,10 +5354,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -3227,10 +5365,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C56" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -3238,10 +5376,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C57" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -3249,10 +5387,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>223</v>
+      </c>
+      <c r="C58" t="s">
         <v>224</v>
-      </c>
-      <c r="C58" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -3260,10 +5398,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C59" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -3271,10 +5409,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C60" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -3282,10 +5420,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -3293,10 +5431,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C62" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -3304,10 +5442,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C63" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -3315,10 +5453,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C64" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -3326,10 +5464,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C65" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -3337,10 +5475,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C66" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -3348,10 +5486,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C67" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -3359,10 +5497,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C68" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -3370,10 +5508,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C69" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -3381,10 +5519,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C70" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -3392,10 +5530,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C71" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -3403,10 +5541,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C72" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -3414,10 +5552,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C73" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -3425,10 +5563,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C74" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -3436,10 +5574,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C75" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -3447,10 +5585,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C76" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -3458,10 +5596,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C77" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -3469,10 +5607,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C78" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -3480,10 +5618,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C79" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
@@ -3491,10 +5629,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C80" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -3502,10 +5640,890 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C81" t="s">
-        <v>301</v>
+        <v>324</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>319</v>
+      </c>
+      <c r="C82" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>320</v>
+      </c>
+      <c r="C83" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>321</v>
+      </c>
+      <c r="C84" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>322</v>
+      </c>
+      <c r="C85" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>337</v>
+      </c>
+      <c r="C86" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>338</v>
+      </c>
+      <c r="C87" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>339</v>
+      </c>
+      <c r="C88" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>340</v>
+      </c>
+      <c r="C89" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>352</v>
+      </c>
+      <c r="C90" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>353</v>
+      </c>
+      <c r="C91" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>354</v>
+      </c>
+      <c r="C92" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>355</v>
+      </c>
+      <c r="C93" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>367</v>
+      </c>
+      <c r="C94" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>368</v>
+      </c>
+      <c r="C95" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>369</v>
+      </c>
+      <c r="C96" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>370</v>
+      </c>
+      <c r="C97" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>383</v>
+      </c>
+      <c r="C98" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>384</v>
+      </c>
+      <c r="C99" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>385</v>
+      </c>
+      <c r="C100" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>389</v>
+      </c>
+      <c r="C101" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>398</v>
+      </c>
+      <c r="C102" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>399</v>
+      </c>
+      <c r="C103" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>400</v>
+      </c>
+      <c r="C104" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>401</v>
+      </c>
+      <c r="C105" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>413</v>
+      </c>
+      <c r="C106" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>414</v>
+      </c>
+      <c r="C107" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>415</v>
+      </c>
+      <c r="C108" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>416</v>
+      </c>
+      <c r="C109" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>428</v>
+      </c>
+      <c r="C110" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>429</v>
+      </c>
+      <c r="C111" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>430</v>
+      </c>
+      <c r="C112" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>431</v>
+      </c>
+      <c r="C113" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>444</v>
+      </c>
+      <c r="C114" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>445</v>
+      </c>
+      <c r="C115" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>446</v>
+      </c>
+      <c r="C116" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>447</v>
+      </c>
+      <c r="C117" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>459</v>
+      </c>
+      <c r="C118" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>460</v>
+      </c>
+      <c r="C119" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>461</v>
+      </c>
+      <c r="C120" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>462</v>
+      </c>
+      <c r="C121" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>475</v>
+      </c>
+      <c r="C122" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>476</v>
+      </c>
+      <c r="C123" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>477</v>
+      </c>
+      <c r="C124" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>478</v>
+      </c>
+      <c r="C125" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>491</v>
+      </c>
+      <c r="C126" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>492</v>
+      </c>
+      <c r="C127" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>493</v>
+      </c>
+      <c r="C128" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>494</v>
+      </c>
+      <c r="C129" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>507</v>
+      </c>
+      <c r="C130" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>508</v>
+      </c>
+      <c r="C131" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>509</v>
+      </c>
+      <c r="C132" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>510</v>
+      </c>
+      <c r="C133" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>522</v>
+      </c>
+      <c r="C134" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>523</v>
+      </c>
+      <c r="C135" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>524</v>
+      </c>
+      <c r="C136" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>525</v>
+      </c>
+      <c r="C137" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>536</v>
+      </c>
+      <c r="C138" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>537</v>
+      </c>
+      <c r="C139" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>538</v>
+      </c>
+      <c r="C140" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>539</v>
+      </c>
+      <c r="C141" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>552</v>
+      </c>
+      <c r="C142" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>553</v>
+      </c>
+      <c r="C143" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>554</v>
+      </c>
+      <c r="C144" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>555</v>
+      </c>
+      <c r="C145" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>566</v>
+      </c>
+      <c r="C146" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>567</v>
+      </c>
+      <c r="C147" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>568</v>
+      </c>
+      <c r="C148" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>569</v>
+      </c>
+      <c r="C149" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>581</v>
+      </c>
+      <c r="C150" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>582</v>
+      </c>
+      <c r="C151" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>583</v>
+      </c>
+      <c r="C152" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>584</v>
+      </c>
+      <c r="C153" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>595</v>
+      </c>
+      <c r="C154" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>596</v>
+      </c>
+      <c r="C155" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>597</v>
+      </c>
+      <c r="C156" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>598</v>
+      </c>
+      <c r="C157" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>611</v>
+      </c>
+      <c r="C158" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
+        <v>612</v>
+      </c>
+      <c r="C159" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>613</v>
+      </c>
+      <c r="C160" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>614</v>
+      </c>
+      <c r="C161" t="s">
+        <v>618</v>
       </c>
     </row>
   </sheetData>
